--- a/docs/StructureDefinition-mars-radiation-risk-assessment.xlsx
+++ b/docs/StructureDefinition-mars-radiation-risk-assessment.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.5.6</t>
+    <t>0.5.8</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-12-30T19:11:20-07:00</t>
+    <t>2026-02-02T11:11:20-06:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-mars-radiation-risk-assessment.xlsx
+++ b/docs/StructureDefinition-mars-radiation-risk-assessment.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.5.8</t>
+    <t>0.5.9</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-02T11:11:20-06:00</t>
+    <t>2026-02-04T10:26:00-06:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-mars-radiation-risk-assessment.xlsx
+++ b/docs/StructureDefinition-mars-radiation-risk-assessment.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.5.12</t>
+    <t>0.6.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-25T00:24:16-05:00</t>
+    <t>2026-05-25T15:07:02-06:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -469,7 +469,7 @@
     <t>Mission Context</t>
   </si>
   <si>
-    <t>Links radiation exposure to specific space missions</t>
+    <t>Links clinical observations and events to specific space missions</t>
   </si>
   <si>
     <t xml:space="preserve">ele-1

--- a/docs/StructureDefinition-mars-radiation-risk-assessment.xlsx
+++ b/docs/StructureDefinition-mars-radiation-risk-assessment.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.6.0</t>
+    <t>0.6.2</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-25T15:07:02-06:00</t>
+    <t>2026-08-03T22:31:50-05:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-mars-radiation-risk-assessment.xlsx
+++ b/docs/StructureDefinition-mars-radiation-risk-assessment.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1540" uniqueCount="332">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1541" uniqueCount="333">
   <si>
     <t>Property</t>
   </si>
@@ -27,13 +27,13 @@
     <t>URL</t>
   </si>
   <si>
-    <t>https://mitre.org/fhir/space-health/StructureDefinition/mars-radiation-risk-assessment</t>
+    <t>https://awatson1978.github.io/aerospace-medicine-ig/StructureDefinition/mars-radiation-risk-assessment</t>
   </si>
   <si>
     <t>Version</t>
   </si>
   <si>
-    <t>0.6.2</t>
+    <t>0.7.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-03T22:31:50-05:00</t>
+    <t>2026-09-02T13:24:45-05:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -91,6 +91,9 @@
   </si>
   <si>
     <t>Copyright</t>
+  </si>
+  <si>
+    <t>Copyright 2022-2026 The MITRE Corporation and Abigail Watson. Licensed under Creative Commons Attribution-NoDerivatives 4.0 International (CC BY-ND 4.0). Approved for Public Release; Distribution Unlimited. Public Release Case Number 25-1124.</t>
   </si>
   <si>
     <t>FHIR Version</t>
@@ -462,7 +465,7 @@
     <t>missionContext</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {http://hl7.org/fhir/uv/aerospace/StructureDefinition/mission-context}
+    <t xml:space="preserve">Extension {https://awatson1978.github.io/aerospace-medicine-ig/StructureDefinition/mission-context}
 </t>
   </si>
   <si>
@@ -1310,54 +1313,56 @@
       <c r="A14" t="s" s="2">
         <v>24</v>
       </c>
-      <c r="B14" s="2"/>
+      <c r="B14" t="s" s="2">
+        <v>25</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
   </sheetData>
@@ -1380,7 +1385,7 @@
     <col min="8" max="8" width="12.6875" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="10.51171875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="74.9921875" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="81.42578125" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -1414,146 +1419,146 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B1" t="s" s="1">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C1" t="s" s="1">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D1" t="s" s="1">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E1" t="s" s="1">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F1" t="s" s="1">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G1" t="s" s="1">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H1" t="s" s="1">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="I1" t="s" s="1">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="J1" t="s" s="1">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="K1" t="s" s="1">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="L1" t="s" s="1">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="M1" t="s" s="1">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="N1" t="s" s="1">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="O1" t="s" s="1">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="P1" t="s" s="1">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="Q1" t="s" s="1">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="R1" t="s" s="1">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="S1" t="s" s="1">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="T1" t="s" s="1">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="U1" t="s" s="1">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="V1" t="s" s="1">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="W1" t="s" s="1">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="X1" t="s" s="1">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="Y1" t="s" s="1">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="Z1" t="s" s="1">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="AA1" t="s" s="1">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="AB1" t="s" s="1">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="AC1" t="s" s="1">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="AD1" t="s" s="1">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="AE1" t="s" s="1">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="AF1" t="s" s="1">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="AG1" t="s" s="1">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="AH1" t="s" s="1">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="AI1" t="s" s="1">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AJ1" t="s" s="1">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="AK1" t="s" s="1">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AL1" t="s" s="1">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AM1" t="s" s="1">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AN1" t="s" s="1">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AO1" t="s" s="1">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="2" hidden="true">
       <c r="A2" t="s" s="2">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="E2" s="2"/>
       <c r="F2" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G2" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H2" t="s" s="2">
         <v>20</v>
@@ -1565,13 +1570,13 @@
         <v>20</v>
       </c>
       <c r="K2" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="L2" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="M2" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="N2" s="2"/>
       <c r="O2" s="2"/>
@@ -1622,31 +1627,31 @@
         <v>20</v>
       </c>
       <c r="AF2" t="s" s="2">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="AG2" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AH2" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AI2" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ2" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AK2" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AL2" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AM2" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AN2" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="AO2" t="s" s="2">
         <v>20</v>
@@ -1654,10 +1659,10 @@
     </row>
     <row r="3" hidden="true">
       <c r="A3" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" t="s" s="2">
@@ -1665,10 +1670,10 @@
       </c>
       <c r="E3" s="2"/>
       <c r="F3" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G3" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H3" t="s" s="2">
         <v>20</v>
@@ -1677,19 +1682,19 @@
         <v>20</v>
       </c>
       <c r="J3" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="K3" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="L3" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="M3" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="N3" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="O3" s="2"/>
       <c r="P3" t="s" s="2">
@@ -1739,13 +1744,13 @@
         <v>20</v>
       </c>
       <c r="AF3" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AG3" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AH3" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="AI3" t="s" s="2">
         <v>20</v>
@@ -1771,10 +1776,10 @@
     </row>
     <row r="4" hidden="true">
       <c r="A4" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" t="s" s="2">
@@ -1782,10 +1787,10 @@
       </c>
       <c r="E4" s="2"/>
       <c r="F4" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G4" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H4" t="s" s="2">
         <v>20</v>
@@ -1794,16 +1799,16 @@
         <v>20</v>
       </c>
       <c r="J4" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="K4" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="L4" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="M4" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="N4" s="2"/>
       <c r="O4" s="2"/>
@@ -1854,19 +1859,19 @@
         <v>20</v>
       </c>
       <c r="AF4" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AG4" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AH4" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="AI4" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ4" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="AK4" t="s" s="2">
         <v>20</v>
@@ -1886,10 +1891,10 @@
     </row>
     <row r="5" hidden="true">
       <c r="A5" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" t="s" s="2">
@@ -1897,31 +1902,31 @@
       </c>
       <c r="E5" s="2"/>
       <c r="F5" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G5" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H5" t="s" s="2">
         <v>20</v>
       </c>
       <c r="I5" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="J5" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="K5" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="L5" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="M5" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="N5" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="O5" s="2"/>
       <c r="P5" t="s" s="2">
@@ -1971,19 +1976,19 @@
         <v>20</v>
       </c>
       <c r="AF5" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="AG5" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AH5" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="AI5" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ5" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="AK5" t="s" s="2">
         <v>20</v>
@@ -2003,10 +2008,10 @@
     </row>
     <row r="6" hidden="true">
       <c r="A6" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
@@ -2014,10 +2019,10 @@
       </c>
       <c r="E6" s="2"/>
       <c r="F6" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G6" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H6" t="s" s="2">
         <v>20</v>
@@ -2029,16 +2034,16 @@
         <v>20</v>
       </c>
       <c r="K6" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="L6" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="M6" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="N6" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="O6" s="2"/>
       <c r="P6" t="s" s="2">
@@ -2064,13 +2069,13 @@
         <v>20</v>
       </c>
       <c r="X6" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="Y6" t="s" s="2">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="Z6" t="s" s="2">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="AA6" t="s" s="2">
         <v>20</v>
@@ -2088,19 +2093,19 @@
         <v>20</v>
       </c>
       <c r="AF6" t="s" s="2">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="AG6" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AH6" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="AI6" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ6" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="AK6" t="s" s="2">
         <v>20</v>
@@ -2120,21 +2125,21 @@
     </row>
     <row r="7" hidden="true">
       <c r="A7" t="s" s="2">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="E7" s="2"/>
       <c r="F7" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G7" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H7" t="s" s="2">
         <v>20</v>
@@ -2146,16 +2151,16 @@
         <v>20</v>
       </c>
       <c r="K7" t="s" s="2">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="L7" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="M7" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="N7" t="s" s="2">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="O7" s="2"/>
       <c r="P7" t="s" s="2">
@@ -2205,19 +2210,19 @@
         <v>20</v>
       </c>
       <c r="AF7" t="s" s="2">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="AG7" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AH7" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="AI7" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ7" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="AK7" t="s" s="2">
         <v>20</v>
@@ -2226,7 +2231,7 @@
         <v>20</v>
       </c>
       <c r="AM7" t="s" s="2">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="AN7" t="s" s="2">
         <v>20</v>
@@ -2237,21 +2242,21 @@
     </row>
     <row r="8" hidden="true">
       <c r="A8" t="s" s="2">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E8" s="2"/>
       <c r="F8" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G8" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H8" t="s" s="2">
         <v>20</v>
@@ -2263,16 +2268,16 @@
         <v>20</v>
       </c>
       <c r="K8" t="s" s="2">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="L8" t="s" s="2">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="M8" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="N8" t="s" s="2">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="O8" s="2"/>
       <c r="P8" t="s" s="2">
@@ -2322,13 +2327,13 @@
         <v>20</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="AG8" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AH8" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AI8" t="s" s="2">
         <v>20</v>
@@ -2343,7 +2348,7 @@
         <v>20</v>
       </c>
       <c r="AM8" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AN8" t="s" s="2">
         <v>20</v>
@@ -2354,10 +2359,10 @@
     </row>
     <row r="9" hidden="true">
       <c r="A9" t="s" s="2">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
@@ -2365,10 +2370,10 @@
       </c>
       <c r="E9" s="2"/>
       <c r="F9" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G9" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H9" t="s" s="2">
         <v>20</v>
@@ -2380,13 +2385,13 @@
         <v>20</v>
       </c>
       <c r="K9" t="s" s="2">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="L9" t="s" s="2">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="M9" t="s" s="2">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="N9" s="2"/>
       <c r="O9" s="2"/>
@@ -2425,29 +2430,29 @@
         <v>20</v>
       </c>
       <c r="AB9" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="AC9" s="2"/>
       <c r="AD9" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE9" t="s" s="2">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="AG9" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AH9" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AI9" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ9" t="s" s="2">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="AK9" t="s" s="2">
         <v>20</v>
@@ -2467,26 +2472,26 @@
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C10" t="s" s="2">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="D10" t="s" s="2">
         <v>20</v>
       </c>
       <c r="E10" s="2"/>
       <c r="F10" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G10" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H10" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="I10" t="s" s="2">
         <v>20</v>
@@ -2495,13 +2500,13 @@
         <v>20</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="N10" s="2"/>
       <c r="O10" s="2"/>
@@ -2552,19 +2557,19 @@
         <v>20</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="AG10" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AH10" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AI10" t="s" s="2">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="AJ10" t="s" s="2">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="AK10" t="s" s="2">
         <v>20</v>
@@ -2584,45 +2589,45 @@
     </row>
     <row r="11" hidden="true">
       <c r="A11" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="E11" s="2"/>
       <c r="F11" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G11" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H11" t="s" s="2">
         <v>20</v>
       </c>
       <c r="I11" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="J11" t="s" s="2">
         <v>20</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="N11" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="O11" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="P11" t="s" s="2">
         <v>20</v>
@@ -2671,19 +2676,19 @@
         <v>20</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="AG11" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AH11" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AI11" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ11" t="s" s="2">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="AK11" t="s" s="2">
         <v>20</v>
@@ -2692,7 +2697,7 @@
         <v>20</v>
       </c>
       <c r="AM11" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AN11" t="s" s="2">
         <v>20</v>
@@ -2703,10 +2708,10 @@
     </row>
     <row r="12" hidden="true">
       <c r="A12" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -2714,10 +2719,10 @@
       </c>
       <c r="E12" s="2"/>
       <c r="F12" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G12" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H12" t="s" s="2">
         <v>20</v>
@@ -2726,16 +2731,16 @@
         <v>20</v>
       </c>
       <c r="J12" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="N12" s="2"/>
       <c r="O12" s="2"/>
@@ -2786,42 +2791,42 @@
         <v>20</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="AG12" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AH12" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AI12" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ12" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="AK12" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="AL12" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AM12" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="AN12" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="AO12" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
     </row>
     <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -2829,10 +2834,10 @@
       </c>
       <c r="E13" s="2"/>
       <c r="F13" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G13" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H13" t="s" s="2">
         <v>20</v>
@@ -2844,13 +2849,13 @@
         <v>20</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="N13" s="2"/>
       <c r="O13" s="2"/>
@@ -2901,22 +2906,22 @@
         <v>20</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="AG13" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AH13" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="AI13" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ13" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="AK13" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="AL13" t="s" s="2">
         <v>20</v>
@@ -2933,10 +2938,10 @@
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -2944,10 +2949,10 @@
       </c>
       <c r="E14" s="2"/>
       <c r="F14" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G14" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H14" t="s" s="2">
         <v>20</v>
@@ -2959,13 +2964,13 @@
         <v>20</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="N14" s="2"/>
       <c r="O14" s="2"/>
@@ -3016,22 +3021,22 @@
         <v>20</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="AG14" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AH14" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="AI14" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ14" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="AK14" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="AL14" t="s" s="2">
         <v>20</v>
@@ -3048,10 +3053,10 @@
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -3059,28 +3064,28 @@
       </c>
       <c r="E15" s="2"/>
       <c r="F15" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="G15" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H15" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="I15" t="s" s="2">
         <v>20</v>
       </c>
       <c r="J15" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="N15" s="2"/>
       <c r="O15" s="2"/>
@@ -3107,13 +3112,13 @@
         <v>20</v>
       </c>
       <c r="X15" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="Y15" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="Z15" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="AA15" t="s" s="2">
         <v>20</v>
@@ -3131,22 +3136,22 @@
         <v>20</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="AG15" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="AH15" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="AI15" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ15" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="AK15" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="AL15" t="s" s="2">
         <v>20</v>
@@ -3158,15 +3163,15 @@
         <v>20</v>
       </c>
       <c r="AO15" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -3174,10 +3179,10 @@
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G16" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H16" t="s" s="2">
         <v>20</v>
@@ -3186,20 +3191,20 @@
         <v>20</v>
       </c>
       <c r="J16" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="N16" s="2"/>
       <c r="O16" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="P16" t="s" s="2">
         <v>20</v>
@@ -3224,10 +3229,10 @@
         <v>20</v>
       </c>
       <c r="X16" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="Y16" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="Z16" t="s" s="2">
         <v>20</v>
@@ -3248,19 +3253,19 @@
         <v>20</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="AG16" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AH16" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="AI16" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ16" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="AK16" t="s" s="2">
         <v>20</v>
@@ -3269,21 +3274,21 @@
         <v>20</v>
       </c>
       <c r="AM16" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="AN16" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AO16" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -3291,28 +3296,28 @@
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G17" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H17" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="I17" t="s" s="2">
         <v>20</v>
       </c>
       <c r="J17" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="N17" s="2"/>
       <c r="O17" s="2"/>
@@ -3363,22 +3368,22 @@
         <v>20</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="AG17" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AH17" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="AI17" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ17" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="AK17" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="AL17" t="s" s="2">
         <v>20</v>
@@ -3390,15 +3395,15 @@
         <v>20</v>
       </c>
       <c r="AO17" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -3406,10 +3411,10 @@
       </c>
       <c r="E18" s="2"/>
       <c r="F18" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G18" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H18" t="s" s="2">
         <v>20</v>
@@ -3421,13 +3426,13 @@
         <v>20</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="N18" s="2"/>
       <c r="O18" s="2"/>
@@ -3478,13 +3483,13 @@
         <v>20</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="AG18" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AH18" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="AI18" t="s" s="2">
         <v>20</v>
@@ -3499,7 +3504,7 @@
         <v>20</v>
       </c>
       <c r="AM18" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="AN18" t="s" s="2">
         <v>20</v>
@@ -3510,21 +3515,21 @@
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G19" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H19" t="s" s="2">
         <v>20</v>
@@ -3536,16 +3541,16 @@
         <v>20</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="N19" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
@@ -3583,31 +3588,31 @@
         <v>20</v>
       </c>
       <c r="AB19" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="AC19" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="AD19" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE19" t="s" s="2">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="AG19" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AH19" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AI19" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ19" t="s" s="2">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="AK19" t="s" s="2">
         <v>20</v>
@@ -3616,7 +3621,7 @@
         <v>20</v>
       </c>
       <c r="AM19" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="AN19" t="s" s="2">
         <v>20</v>
@@ -3627,10 +3632,10 @@
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -3638,10 +3643,10 @@
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G20" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H20" t="s" s="2">
         <v>20</v>
@@ -3650,22 +3655,22 @@
         <v>20</v>
       </c>
       <c r="J20" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="N20" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="O20" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="P20" t="s" s="2">
         <v>20</v>
@@ -3714,28 +3719,28 @@
         <v>20</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="AG20" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AH20" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AI20" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ20" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="AK20" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL20" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="AM20" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="AN20" t="s" s="2">
         <v>20</v>
@@ -3746,10 +3751,10 @@
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -3757,10 +3762,10 @@
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G21" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H21" t="s" s="2">
         <v>20</v>
@@ -3769,22 +3774,22 @@
         <v>20</v>
       </c>
       <c r="J21" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="N21" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="O21" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="P21" t="s" s="2">
         <v>20</v>
@@ -3794,7 +3799,7 @@
         <v>20</v>
       </c>
       <c r="S21" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="T21" t="s" s="2">
         <v>20</v>
@@ -3833,28 +3838,28 @@
         <v>20</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="AG21" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AH21" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="AI21" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ21" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="AK21" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="AN21" t="s" s="2">
         <v>20</v>
@@ -3865,10 +3870,10 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -3876,28 +3881,28 @@
       </c>
       <c r="E22" s="2"/>
       <c r="F22" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="G22" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H22" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="I22" t="s" s="2">
         <v>20</v>
       </c>
       <c r="J22" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" s="2"/>
@@ -3948,42 +3953,42 @@
         <v>20</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="AG22" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="AH22" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="AI22" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ22" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="AL22" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="AN22" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="AO22" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -3991,10 +3996,10 @@
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G23" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H23" t="s" s="2">
         <v>20</v>
@@ -4003,16 +4008,16 @@
         <v>20</v>
       </c>
       <c r="J23" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" s="2"/>
@@ -4063,42 +4068,42 @@
         <v>20</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="AG23" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AH23" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="AI23" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ23" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="AL23" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="AN23" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AO23" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -4106,10 +4111,10 @@
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G24" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H24" t="s" s="2">
         <v>20</v>
@@ -4118,20 +4123,20 @@
         <v>20</v>
       </c>
       <c r="J24" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="P24" t="s" s="2">
         <v>20</v>
@@ -4180,42 +4185,42 @@
         <v>20</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="AG24" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AH24" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="AI24" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ24" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="AL24" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="AN24" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AO24" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4223,10 +4228,10 @@
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G25" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H25" t="s" s="2">
         <v>20</v>
@@ -4235,16 +4240,16 @@
         <v>20</v>
       </c>
       <c r="J25" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="N25" s="2"/>
       <c r="O25" s="2"/>
@@ -4295,19 +4300,19 @@
         <v>20</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="AG25" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AH25" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="AI25" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ25" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="AK25" t="s" s="2">
         <v>20</v>
@@ -4316,7 +4321,7 @@
         <v>20</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="AN25" t="s" s="2">
         <v>20</v>
@@ -4327,10 +4332,10 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4338,10 +4343,10 @@
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G26" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H26" t="s" s="2">
         <v>20</v>
@@ -4350,16 +4355,16 @@
         <v>20</v>
       </c>
       <c r="J26" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="N26" s="2"/>
       <c r="O26" s="2"/>
@@ -4410,42 +4415,42 @@
         <v>20</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="AG26" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AH26" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="AI26" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ26" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="AL26" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="AO26" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -4453,10 +4458,10 @@
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G27" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H27" t="s" s="2">
         <v>20</v>
@@ -4468,13 +4473,13 @@
         <v>20</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="N27" s="2"/>
       <c r="O27" s="2"/>
@@ -4525,22 +4530,22 @@
         <v>20</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="AG27" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AH27" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AI27" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ27" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="AL27" t="s" s="2">
         <v>20</v>
@@ -4552,15 +4557,15 @@
         <v>20</v>
       </c>
       <c r="AO27" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -4568,10 +4573,10 @@
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G28" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H28" t="s" s="2">
         <v>20</v>
@@ -4583,13 +4588,13 @@
         <v>20</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="N28" s="2"/>
       <c r="O28" s="2"/>
@@ -4640,42 +4645,42 @@
         <v>20</v>
       </c>
       <c r="AF28" t="s" s="2">
+        <v>264</v>
+      </c>
+      <c r="AG28" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH28" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI28" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ28" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AK28" t="s" s="2">
+        <v>267</v>
+      </c>
+      <c r="AL28" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AM28" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AN28" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AO28" t="s" s="2">
         <v>263</v>
-      </c>
-      <c r="AG28" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH28" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AI28" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AJ28" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="AK28" t="s" s="2">
-        <v>266</v>
-      </c>
-      <c r="AL28" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AM28" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AN28" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AO28" t="s" s="2">
-        <v>262</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -4683,13 +4688,13 @@
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G29" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H29" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="I29" t="s" s="2">
         <v>20</v>
@@ -4698,13 +4703,13 @@
         <v>20</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="N29" s="2"/>
       <c r="O29" s="2"/>
@@ -4755,19 +4760,19 @@
         <v>20</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="AG29" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AH29" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AI29" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ29" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="AK29" t="s" s="2">
         <v>20</v>
@@ -4776,10 +4781,10 @@
         <v>20</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="AO29" t="s" s="2">
         <v>20</v>
@@ -4787,10 +4792,10 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -4798,13 +4803,13 @@
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G30" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H30" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="I30" t="s" s="2">
         <v>20</v>
@@ -4813,16 +4818,16 @@
         <v>20</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
@@ -4872,19 +4877,19 @@
         <v>20</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="AG30" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AH30" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AI30" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ30" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="AK30" t="s" s="2">
         <v>20</v>
@@ -4893,7 +4898,7 @@
         <v>20</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="AN30" t="s" s="2">
         <v>20</v>
@@ -4904,10 +4909,10 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -4915,10 +4920,10 @@
       </c>
       <c r="E31" s="2"/>
       <c r="F31" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G31" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H31" t="s" s="2">
         <v>20</v>
@@ -4930,13 +4935,13 @@
         <v>20</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
@@ -4987,13 +4992,13 @@
         <v>20</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="AG31" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AH31" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="AI31" t="s" s="2">
         <v>20</v>
@@ -5008,7 +5013,7 @@
         <v>20</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="AN31" t="s" s="2">
         <v>20</v>
@@ -5019,21 +5024,21 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G32" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H32" t="s" s="2">
         <v>20</v>
@@ -5045,16 +5050,16 @@
         <v>20</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
@@ -5104,19 +5109,19 @@
         <v>20</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="AG32" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AH32" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AI32" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="AK32" t="s" s="2">
         <v>20</v>
@@ -5125,7 +5130,7 @@
         <v>20</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="AN32" t="s" s="2">
         <v>20</v>
@@ -5136,45 +5141,45 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G33" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H33" t="s" s="2">
         <v>20</v>
       </c>
       <c r="I33" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="J33" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="O33" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="P33" t="s" s="2">
         <v>20</v>
@@ -5223,19 +5228,19 @@
         <v>20</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="AG33" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AH33" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AI33" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="AK33" t="s" s="2">
         <v>20</v>
@@ -5244,7 +5249,7 @@
         <v>20</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AN33" t="s" s="2">
         <v>20</v>
@@ -5255,10 +5260,10 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5266,13 +5271,13 @@
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G34" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H34" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="I34" t="s" s="2">
         <v>20</v>
@@ -5281,13 +5286,13 @@
         <v>20</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" s="2"/>
@@ -5314,10 +5319,10 @@
         <v>20</v>
       </c>
       <c r="X34" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="Y34" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="Z34" t="s" s="2">
         <v>20</v>
@@ -5338,19 +5343,19 @@
         <v>20</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="AG34" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AH34" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="AI34" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="AK34" t="s" s="2">
         <v>20</v>
@@ -5359,10 +5364,10 @@
         <v>20</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="AO34" t="s" s="2">
         <v>20</v>
@@ -5370,10 +5375,10 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5381,13 +5386,13 @@
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G35" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H35" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="I35" t="s" s="2">
         <v>20</v>
@@ -5396,16 +5401,16 @@
         <v>20</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
@@ -5455,19 +5460,19 @@
         <v>20</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="AG35" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AH35" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="AI35" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ35" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="AK35" t="s" s="2">
         <v>20</v>
@@ -5476,10 +5481,10 @@
         <v>20</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="AO35" t="s" s="2">
         <v>20</v>
@@ -5487,10 +5492,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -5498,10 +5503,10 @@
       </c>
       <c r="E36" s="2"/>
       <c r="F36" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G36" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H36" t="s" s="2">
         <v>20</v>
@@ -5513,13 +5518,13 @@
         <v>20</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
@@ -5546,13 +5551,13 @@
         <v>20</v>
       </c>
       <c r="X36" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="Y36" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="Z36" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="AA36" t="s" s="2">
         <v>20</v>
@@ -5570,19 +5575,19 @@
         <v>20</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="AG36" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AH36" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="AI36" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ36" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="AK36" t="s" s="2">
         <v>20</v>
@@ -5602,10 +5607,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -5613,10 +5618,10 @@
       </c>
       <c r="E37" s="2"/>
       <c r="F37" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G37" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H37" t="s" s="2">
         <v>20</v>
@@ -5628,17 +5633,17 @@
         <v>20</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="P37" t="s" s="2">
         <v>20</v>
@@ -5687,19 +5692,19 @@
         <v>20</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="AG37" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AH37" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="AI37" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ37" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="AK37" t="s" s="2">
         <v>20</v>
@@ -5708,7 +5713,7 @@
         <v>20</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="AN37" t="s" s="2">
         <v>20</v>
@@ -5719,10 +5724,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -5730,10 +5735,10 @@
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G38" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H38" t="s" s="2">
         <v>20</v>
@@ -5745,16 +5750,16 @@
         <v>20</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
@@ -5804,19 +5809,19 @@
         <v>20</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="AG38" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AH38" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="AI38" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ38" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="AK38" t="s" s="2">
         <v>20</v>
@@ -5825,7 +5830,7 @@
         <v>20</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="AN38" t="s" s="2">
         <v>20</v>
@@ -5836,10 +5841,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -5847,10 +5852,10 @@
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G39" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H39" t="s" s="2">
         <v>20</v>
@@ -5862,13 +5867,13 @@
         <v>20</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" s="2"/>
@@ -5919,19 +5924,19 @@
         <v>20</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="AG39" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AH39" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="AI39" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="AK39" t="s" s="2">
         <v>20</v>
@@ -5940,10 +5945,10 @@
         <v>20</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="AO39" t="s" s="2">
         <v>20</v>
@@ -5951,10 +5956,10 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -5962,13 +5967,13 @@
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G40" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H40" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="I40" t="s" s="2">
         <v>20</v>
@@ -5977,17 +5982,17 @@
         <v>20</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="P40" t="s" s="2">
         <v>20</v>
@@ -6036,19 +6041,19 @@
         <v>20</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="AG40" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AH40" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="AI40" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="AK40" t="s" s="2">
         <v>20</v>
@@ -6057,7 +6062,7 @@
         <v>20</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="AN40" t="s" s="2">
         <v>20</v>
@@ -6068,10 +6073,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6079,10 +6084,10 @@
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G41" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H41" t="s" s="2">
         <v>20</v>
@@ -6094,13 +6099,13 @@
         <v>20</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" s="2"/>
@@ -6151,22 +6156,22 @@
         <v>20</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="AG41" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AH41" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AI41" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AL41" t="s" s="2">
         <v>20</v>
